--- a/Data/BaseData/df_tek_weights_annuities.xlsx
+++ b/Data/BaseData/df_tek_weights_annuities.xlsx
@@ -12,12 +12,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t xml:space="preserve">orgnr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category</t>
+  </si>
   <si>
     <t xml:space="preserve">y</t>
   </si>
   <si>
-    <t xml:space="preserve">kpi</t>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">linjer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jordkabler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sjøkabler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hovedtransformator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">annet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">målere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">annet, kundespesifikke anlegg</t>
   </si>
 </sst>
 </file>
@@ -353,621 +380,4127 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1949</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1.051</v>
+        <v>882783022</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.026516785813893</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1950</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1.106703</v>
+        <v>882783022</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.121460474859217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1951</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1.175318586</v>
+        <v>882783022</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.052648404202678</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1952</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1.254064931262</v>
+        <v>882783022</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.042020178462342</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1953</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1.34059541151908</v>
+        <v>882783022</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0216309586421595</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1954</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1.43577768573693</v>
+        <v>882783022</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.121136793149016</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1955</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1.53915367910999</v>
+        <v>882783022</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0224913269556155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1956</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1.65459020504324</v>
+        <v>882783022</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.121709741460683</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1957</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1.78199365083157</v>
+        <v>882783022</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0181232526622267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1958</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1.92633513654893</v>
+        <v>882783022</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0177901873318196</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1959</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2.08622095288249</v>
+        <v>882783022</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0142316355699789</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1960</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2.25937729197173</v>
+        <v>882783022</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0691503826719421</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1961</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2.45142436178933</v>
+        <v>882783022</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0405776890134523</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1962</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2.66960112998858</v>
+        <v>882783022</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.00361130342932792</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1963</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2.91520443394753</v>
+        <v>882783022</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0418548193554916</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1964</v>
-      </c>
-      <c r="B17" t="n">
-        <v>3.19797926404044</v>
+        <v>882783022</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.100311777338454</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1965</v>
-      </c>
-      <c r="B18" t="n">
-        <v>3.52097516970853</v>
+        <v>882783022</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.00479266014923145</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1966</v>
-      </c>
-      <c r="B19" t="n">
-        <v>3.88715658735821</v>
+        <v>882783022</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0763809293934611</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1967</v>
-      </c>
-      <c r="B20" t="n">
-        <v>4.31085665538026</v>
+        <v>882783022</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0378822409148111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1968</v>
-      </c>
-      <c r="B21" t="n">
-        <v>4.79798345743823</v>
+        <v>882783022</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0276010684128119</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1969</v>
-      </c>
-      <c r="B22" t="n">
-        <v>5.35454953850106</v>
+        <v>882783022</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.0180773902113869</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1970</v>
-      </c>
-      <c r="B23" t="n">
-        <v>6.0399318794292</v>
+        <v>882783022</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.00164827856679511</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1971</v>
-      </c>
-      <c r="B24" t="n">
-        <v>6.40836772407438</v>
+        <v>882783022</v>
+      </c>
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0286532891318285</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1972</v>
-      </c>
-      <c r="B25" t="n">
-        <v>6.71596937482995</v>
+        <v>882783022</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0846912791352143</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1973</v>
-      </c>
-      <c r="B26" t="n">
-        <v>7.14579141481907</v>
+        <v>882783022</v>
+      </c>
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0369329623174452</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1974</v>
-      </c>
-      <c r="B27" t="n">
-        <v>8.32484699826422</v>
+        <v>882783022</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0609623099514925</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1975</v>
-      </c>
-      <c r="B28" t="n">
-        <v>9.14900685109238</v>
+        <v>882783022</v>
+      </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.00619115581021445</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1976</v>
-      </c>
-      <c r="B29" t="n">
-        <v>10.0090134950951</v>
+        <v>882783022</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.06767799886855</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1977</v>
-      </c>
-      <c r="B30" t="n">
-        <v>10.8597796421781</v>
+        <v>882783022</v>
+      </c>
+      <c r="B30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0145624781693909</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1978</v>
-      </c>
-      <c r="B31" t="n">
-        <v>11.2398719296544</v>
+        <v>882783022</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.107029060624129</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1979</v>
-      </c>
-      <c r="B32" t="n">
-        <v>11.869304757715</v>
+        <v>882783022</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.00175344718544912</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1980</v>
-      </c>
-      <c r="B33" t="n">
-        <v>13.24614410961</v>
+        <v>882783022</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0938769048827887</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1981</v>
-      </c>
-      <c r="B34" t="n">
-        <v>14.4118047912556</v>
+        <v>882783022</v>
+      </c>
+      <c r="B34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.010784144953721</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1982</v>
-      </c>
-      <c r="B35" t="n">
-        <v>15.7088672224686</v>
+        <v>882783022</v>
+      </c>
+      <c r="B35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.062238073035475</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1983</v>
-      </c>
-      <c r="B36" t="n">
-        <v>16.9812854674886</v>
+        <v>882783022</v>
+      </c>
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0460640980164097</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1984</v>
-      </c>
-      <c r="B37" t="n">
-        <v>18.1020503083429</v>
+        <v>882783022</v>
+      </c>
+      <c r="B37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.00839756660520668</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1985</v>
-      </c>
-      <c r="B38" t="n">
-        <v>18.8804384716016</v>
+        <v>882783022</v>
+      </c>
+      <c r="B38" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.0384373576242082</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1986</v>
-      </c>
-      <c r="B39" t="n">
-        <v>20.2209496030853</v>
+        <v>882783022</v>
+      </c>
+      <c r="B39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0801361098734207</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1987</v>
-      </c>
-      <c r="B40" t="n">
-        <v>22.0610560169661</v>
+        <v>882783022</v>
+      </c>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.111052567728837</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1988</v>
-      </c>
-      <c r="B41" t="n">
-        <v>23.1420477617974</v>
+        <v>882783022</v>
+      </c>
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.0565703360551647</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1989</v>
-      </c>
-      <c r="B42" t="n">
-        <v>23.30404209613</v>
+        <v>882783022</v>
+      </c>
+      <c r="B42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.0170960620866967</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1990</v>
-      </c>
-      <c r="B43" t="n">
-        <v>22.954481464688</v>
+        <v>882783022</v>
+      </c>
+      <c r="B43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.0652445193775623</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1991</v>
-      </c>
-      <c r="B44" t="n">
-        <v>23.0692538720115</v>
+        <v>882783022</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.0207474931900724</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1992</v>
-      </c>
-      <c r="B45" t="n">
-        <v>22.9077690949074</v>
+        <v>882783022</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.0415084940017185</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1993</v>
-      </c>
-      <c r="B46" t="n">
-        <v>22.999400171287</v>
+        <v>882783022</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.0409897773860574</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1994</v>
-      </c>
-      <c r="B47" t="n">
-        <v>23.5973845757405</v>
+        <v>882783022</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.0262654151363288</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1995</v>
-      </c>
-      <c r="B48" t="n">
-        <v>24.1401244209825</v>
+        <v>882783022</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.0793641531344508</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B49" t="n">
-        <v>24.0677040477196</v>
+        <v>882783022</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.0523005253632343</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1997</v>
-      </c>
-      <c r="B50" t="n">
-        <v>24.115839455815</v>
+        <v>882783022</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.010510708573683</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1998</v>
-      </c>
-      <c r="B51" t="n">
-        <v>24.8875463184011</v>
+        <v>882783022</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.0348929223664372</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B52" t="n">
-        <v>25.2857470594955</v>
+        <v>882783022</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.0754128723617222</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B53" t="n">
-        <v>25.9937479771614</v>
+        <v>882783022</v>
+      </c>
+      <c r="B53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.0385835186405359</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B54" t="n">
-        <v>27.0854853922022</v>
+        <v>882783022</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.0749058046821884</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B55" t="n">
-        <v>26.8688015090645</v>
+        <v>882783022</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.049301874969472</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B56" t="n">
-        <v>26.4120318834104</v>
+        <v>882783022</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.0521061568954815</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B57" t="n">
-        <v>27.4685131587469</v>
+        <v>882783022</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.0716881911107422</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B58" t="n">
-        <v>28.320037066668</v>
+        <v>882783022</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.0414668128744828</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B59" t="n">
-        <v>29.4811585864014</v>
+        <v>882783022</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.081130238955205</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B60" t="n">
-        <v>31.1615846258263</v>
+        <v>882783022</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.0267553643856984</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B61" t="n">
-        <v>32.9066333648726</v>
+        <v>882783022</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.0397038129436008</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B62" t="n">
-        <v>33.4331394987105</v>
+        <v>882783022</v>
+      </c>
+      <c r="B62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.0294442994849758</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B63" t="n">
-        <v>33.1991075222195</v>
+        <v>882783022</v>
+      </c>
+      <c r="B63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.0517543687531193</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B64" t="n">
-        <v>34.3610762854972</v>
+        <v>882783022</v>
+      </c>
+      <c r="B64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.0611671947907934</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B65" t="n">
-        <v>35.2201031926346</v>
+        <v>882783022</v>
+      </c>
+      <c r="B65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.0321760970000752</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B66" t="n">
-        <v>34.8326820575157</v>
+        <v>882783022</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.0641634227396953</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B67" t="n">
-        <v>35.8428298371836</v>
+        <v>882783022</v>
+      </c>
+      <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.0340278705716004</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B68" t="n">
-        <v>37.3840715201825</v>
+        <v>882783022</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.0517994236395562</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B69" t="n">
-        <v>38.3186733081871</v>
+        <v>882783022</v>
+      </c>
+      <c r="B69" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.0698670972520929</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B70" t="n">
-        <v>39.0850467743508</v>
+        <v>882783022</v>
+      </c>
+      <c r="B70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.0500446078155816</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B71" t="n">
-        <v>40.1012579904839</v>
+        <v>882783022</v>
+      </c>
+      <c r="B71" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.025170191776626</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B72" t="n">
-        <v>41.183991956227</v>
+        <v>882783022</v>
+      </c>
+      <c r="B72" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.0789852099893787</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B73" t="n">
-        <v>43.9845034092504</v>
+        <v>882783022</v>
+      </c>
+      <c r="B73" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.00761309661841974</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B74" t="n">
-        <v>45.479976525165</v>
+        <v>882783022</v>
+      </c>
+      <c r="B74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.0319555144191408</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B75" t="n">
-        <v>49.7550943185305</v>
+        <v>882783022</v>
+      </c>
+      <c r="B75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.0740128484704195</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B76" t="n">
-        <v>53.4369712981017</v>
+        <v>882783022</v>
+      </c>
+      <c r="B76" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.0520623884722775</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B77" t="n">
-        <v>55.7881980352182</v>
+        <v>882783022</v>
+      </c>
+      <c r="B77" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.01578744578996</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B78" t="n">
-        <v>57.5734203723452</v>
+        <v>882783022</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.051999194509531</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B79" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.0509701592002244</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B80" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.0775138110066698</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B81" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.0180215254167696</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.0875427472222856</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B83" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.0892392819813608</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B84" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.00431911084477509</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B85" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.0327289552635597</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B86" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.0116556552235813</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B87" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.0637914661054857</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B88" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.0624563163177484</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.0639021799103367</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B90" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.0882518191162328</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B91" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.0656377813609773</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B92" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.000973403180279225</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B93" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.0238385857473922</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B94" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.0682797688023921</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B95" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.0527155160343872</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B96" t="s">
+        <v>8</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.0710995463574711</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B97" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.0558649799178195</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B98" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.0289828170731281</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B99" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.0946605048263523</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B100" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.0299650873381466</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B101" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.0858305749134894</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B102" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.0293405438301701</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B103" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.027351606978918</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B104" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.0191408193796185</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B105" t="s">
+        <v>8</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.023805311696621</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B106" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.0324557158894525</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B107" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.0306776408532033</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B108" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.0146060774504828</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B109" t="s">
+        <v>9</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.0122417964979888</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B110" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.0410248909508379</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B111" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.00363994845391979</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B112" t="s">
+        <v>9</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.0671895107817064</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B113" t="s">
+        <v>9</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.00949194972457822</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B114" t="s">
+        <v>9</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.0895140670196031</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B115" t="s">
+        <v>9</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.0114746361254182</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B116" t="s">
+        <v>9</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.0206905769779351</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B117" t="s">
+        <v>9</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.0860083918824352</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B118" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.0890947276454374</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B119" t="s">
+        <v>9</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.0262951478386577</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B120" t="s">
+        <v>9</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.0116303712404678</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B121" t="s">
+        <v>9</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.0750886077753703</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B122" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.0701072653793742</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B123" t="s">
+        <v>9</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.0862802819739292</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B124" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.0936862793791898</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B125" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.0887657601094677</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B126" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.0457915724658325</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B127" t="s">
+        <v>9</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.0267004994741647</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B128" t="s">
+        <v>10</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.0309441397084687</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B129" t="s">
+        <v>10</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.0162591659071979</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B130" t="s">
+        <v>10</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.00408875580240426</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B131" t="s">
+        <v>10</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.0223677299199282</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B132" t="s">
+        <v>10</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.0828669448370586</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B133" t="s">
+        <v>10</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.0537417066409179</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B134" t="s">
+        <v>10</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.0935048891425784</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B135" t="s">
+        <v>10</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.0849878450072663</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B136" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.00467906323357567</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B137" t="s">
+        <v>10</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.0466259254967591</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B138" t="s">
+        <v>10</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.02710985510937</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B139" t="s">
+        <v>10</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.0311464344032987</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B140" t="s">
+        <v>10</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.05186164013029</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B141" t="s">
+        <v>10</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.018513343573523</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B142" t="s">
+        <v>10</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.0776606181337748</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B143" t="s">
+        <v>10</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.0205734515342359</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B144" t="s">
+        <v>10</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.026457953694288</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B145" t="s">
+        <v>10</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.101426869897496</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B146" t="s">
+        <v>10</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.0825350867527347</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B147" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.0565669208279124</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>882783022</v>
+      </c>
+      <c r="B148" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.0660816602469212</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B149" t="s">
+        <v>4</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.0469806554675214</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B150" t="s">
+        <v>4</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.00884135779077938</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B151" t="s">
+        <v>4</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.0669252280043841</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B152" t="s">
+        <v>4</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.0469933482536151</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B153" t="s">
+        <v>4</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.0175871972168087</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B154" t="s">
+        <v>4</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.0621133648286245</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B155" t="s">
+        <v>4</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.0254574354004905</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B156" t="s">
+        <v>4</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.0405636061416529</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B157" t="s">
+        <v>4</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.0820116235251138</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B158" t="s">
+        <v>4</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.0351435127648924</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B159" t="s">
+        <v>4</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0.020252285393694</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B160" t="s">
+        <v>4</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.0179927174785754</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B161" t="s">
+        <v>4</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.0571032440206546</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B162" t="s">
+        <v>4</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.0812246459567636</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B163" t="s">
+        <v>4</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.039529011799811</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B164" t="s">
+        <v>4</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.0640974982012236</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B165" t="s">
+        <v>4</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.0475900436553731</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B166" t="s">
+        <v>4</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.0800419230444072</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B167" t="s">
+        <v>4</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.0660365411054624</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B168" t="s">
+        <v>4</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.0440759459706727</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B169" t="s">
+        <v>4</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.0494388139794799</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B170" t="s">
+        <v>5</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.0535404788586779</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B171" t="s">
+        <v>5</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.0265073889971977</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B172" t="s">
+        <v>5</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.0174956451222389</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B173" t="s">
+        <v>5</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.0716690785923608</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B174" t="s">
+        <v>5</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.0535849634283819</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B175" t="s">
+        <v>5</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.0881300924482049</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B176" t="s">
+        <v>5</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.0603837126090706</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B177" t="s">
+        <v>5</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.0662505350759659</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B178" t="s">
+        <v>5</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.045306927559524</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B179" t="s">
+        <v>5</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.0803906805769086</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B180" t="s">
+        <v>5</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.0399282307743008</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B181" t="s">
+        <v>5</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.00296789224175008</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B182" t="s">
+        <v>5</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.0244058496026698</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B183" t="s">
+        <v>5</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.0316570844153308</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B184" t="s">
+        <v>5</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.0126261299447426</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B185" t="s">
+        <v>5</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.0472284030469354</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B186" t="s">
+        <v>5</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.0758359705434709</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B187" t="s">
+        <v>5</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.0318753367487673</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B188" t="s">
+        <v>5</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.0481146669107819</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B189" t="s">
+        <v>5</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0.0467454962433505</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B190" t="s">
+        <v>5</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.0753554362593686</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B191" t="s">
+        <v>6</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.0704141576189531</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B192" t="s">
+        <v>6</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.00226293787890939</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B193" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.0445984664037017</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B194" t="s">
+        <v>6</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.0723312328511921</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B195" t="s">
+        <v>6</v>
+      </c>
+      <c r="C195" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.0479804436074177</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B196" t="s">
+        <v>6</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0.0234887268638472</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B197" t="s">
+        <v>6</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0.0303545699426469</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B198" t="s">
+        <v>6</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.0325158552676695</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B199" t="s">
+        <v>6</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.0378071717493159</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B200" t="s">
+        <v>6</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.0808998532825587</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B201" t="s">
+        <v>6</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.0690826211742652</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B202" t="s">
+        <v>6</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.0649858776796588</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B203" t="s">
+        <v>6</v>
+      </c>
+      <c r="C203" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0.0247295684595942</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B204" t="s">
+        <v>6</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.0402358507087581</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B205" t="s">
+        <v>6</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.0253254099178223</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B206" t="s">
+        <v>6</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.061327124381001</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B207" t="s">
+        <v>6</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.0722896299107833</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B208" t="s">
+        <v>6</v>
+      </c>
+      <c r="C208" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.0577038597611991</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B209" t="s">
+        <v>6</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.0364201897154369</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B210" t="s">
+        <v>6</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.083834137203018</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B211" t="s">
+        <v>6</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.0214123156222509</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B212" t="s">
+        <v>7</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.0544322995950375</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B213" t="s">
+        <v>7</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.0468338900287736</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B214" t="s">
+        <v>7</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.0727540483452354</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B215" t="s">
+        <v>7</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.009402514923937</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B216" t="s">
+        <v>7</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.0647437983528668</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B217" t="s">
+        <v>7</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.0593812560431564</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B218" t="s">
+        <v>7</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.0602438662218632</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B219" t="s">
+        <v>7</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0.0611859140165354</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B220" t="s">
+        <v>7</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0.0537112107844924</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B221" t="s">
+        <v>7</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.0720597283971836</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B222" t="s">
+        <v>7</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.0468553874265758</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B223" t="s">
+        <v>7</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.048435063239</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B224" t="s">
+        <v>7</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.038730140595902</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B225" t="s">
+        <v>7</v>
+      </c>
+      <c r="C225" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.0232731372945311</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B226" t="s">
+        <v>7</v>
+      </c>
+      <c r="C226" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.056285837851852</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B227" t="s">
+        <v>7</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.0385798052640912</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B228" t="s">
+        <v>7</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.0536796660006239</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B229" t="s">
+        <v>7</v>
+      </c>
+      <c r="C229" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.0225527129574805</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B230" t="s">
+        <v>7</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.0296269688734355</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B231" t="s">
+        <v>7</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.0149832401511802</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B232" t="s">
+        <v>7</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.0722495136362466</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B233" t="s">
+        <v>8</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.054595672640312</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B234" t="s">
+        <v>8</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.0946110220658395</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B235" t="s">
+        <v>8</v>
+      </c>
+      <c r="C235" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.0556419180770918</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B236" t="s">
+        <v>8</v>
+      </c>
+      <c r="C236" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.0423519460882517</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B237" t="s">
+        <v>8</v>
+      </c>
+      <c r="C237" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.0220517417864039</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B238" t="s">
+        <v>8</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.0079253318725757</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B239" t="s">
+        <v>8</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.082020330356643</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B240" t="s">
+        <v>8</v>
+      </c>
+      <c r="C240" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.0226364674129256</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B241" t="s">
+        <v>8</v>
+      </c>
+      <c r="C241" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.0953230203411726</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B242" t="s">
+        <v>8</v>
+      </c>
+      <c r="C242" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.0580617102825641</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B243" t="s">
+        <v>8</v>
+      </c>
+      <c r="C243" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.0963429737283279</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B244" t="s">
+        <v>8</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.036231983894895</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B245" t="s">
+        <v>8</v>
+      </c>
+      <c r="C245" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.0535499801208059</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B246" t="s">
+        <v>8</v>
+      </c>
+      <c r="C246" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.0414260718065482</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B247" t="s">
+        <v>8</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.0555517281914735</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B248" t="s">
+        <v>8</v>
+      </c>
+      <c r="C248" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.0417215843032436</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B249" t="s">
+        <v>8</v>
+      </c>
+      <c r="C249" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.0216896209282725</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B250" t="s">
+        <v>8</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.00819800521143244</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B251" t="s">
+        <v>8</v>
+      </c>
+      <c r="C251" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.0614766203486478</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B252" t="s">
+        <v>8</v>
+      </c>
+      <c r="C252" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.0415777532217639</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B253" t="s">
+        <v>8</v>
+      </c>
+      <c r="C253" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.0070145173208092</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B254" t="s">
+        <v>9</v>
+      </c>
+      <c r="C254" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.0348877431627973</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B255" t="s">
+        <v>9</v>
+      </c>
+      <c r="C255" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.0369576132238411</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B256" t="s">
+        <v>9</v>
+      </c>
+      <c r="C256" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.00860713030904076</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B257" t="s">
+        <v>9</v>
+      </c>
+      <c r="C257" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.074443517798581</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B258" t="s">
+        <v>9</v>
+      </c>
+      <c r="C258" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0.0346853612200286</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B259" t="s">
+        <v>9</v>
+      </c>
+      <c r="C259" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0.000433948451494464</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B260" t="s">
+        <v>9</v>
+      </c>
+      <c r="C260" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.0779384463343718</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B261" t="s">
+        <v>9</v>
+      </c>
+      <c r="C261" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.0687546095884721</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B262" t="s">
+        <v>9</v>
+      </c>
+      <c r="C262" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0.111666957730003</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B263" t="s">
+        <v>9</v>
+      </c>
+      <c r="C263" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0.00390762932722607</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B264" t="s">
+        <v>9</v>
+      </c>
+      <c r="C264" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0.0792939430586211</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B265" t="s">
+        <v>9</v>
+      </c>
+      <c r="C265" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0.035487078414258</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B266" t="s">
+        <v>9</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0.0159453890239184</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B267" t="s">
+        <v>9</v>
+      </c>
+      <c r="C267" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0.0133140067035171</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B268" t="s">
+        <v>9</v>
+      </c>
+      <c r="C268" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0.0989124351566377</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B269" t="s">
+        <v>9</v>
+      </c>
+      <c r="C269" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0.00211011322104908</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B270" t="s">
+        <v>9</v>
+      </c>
+      <c r="C270" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0.00653912920382864</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B271" t="s">
+        <v>9</v>
+      </c>
+      <c r="C271" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0.0988413929490822</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B272" t="s">
+        <v>9</v>
+      </c>
+      <c r="C272" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0.0472294608094491</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B273" t="s">
+        <v>9</v>
+      </c>
+      <c r="C273" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0.100339885756946</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B274" t="s">
+        <v>9</v>
+      </c>
+      <c r="C274" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.0497042085568359</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B275" t="s">
+        <v>10</v>
+      </c>
+      <c r="C275" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0.0773421815232204</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B276" t="s">
+        <v>10</v>
+      </c>
+      <c r="C276" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0.0313530287554054</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B277" t="s">
+        <v>10</v>
+      </c>
+      <c r="C277" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0.0729938168213414</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B278" t="s">
+        <v>10</v>
+      </c>
+      <c r="C278" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0.0563169491957595</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B279" t="s">
+        <v>10</v>
+      </c>
+      <c r="C279" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0.0683238386111716</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B280" t="s">
+        <v>10</v>
+      </c>
+      <c r="C280" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0.0411554762329115</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B281" t="s">
+        <v>10</v>
+      </c>
+      <c r="C281" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.0331163950843023</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B282" t="s">
+        <v>10</v>
+      </c>
+      <c r="C282" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0.073170299027509</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B283" t="s">
+        <v>10</v>
+      </c>
+      <c r="C283" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0.0408715588111536</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B284" t="s">
+        <v>10</v>
+      </c>
+      <c r="C284" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0.0540629793533976</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B285" t="s">
+        <v>10</v>
+      </c>
+      <c r="C285" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0.0111941320314657</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B286" t="s">
+        <v>10</v>
+      </c>
+      <c r="C286" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0.0292077615941806</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B287" t="s">
+        <v>10</v>
+      </c>
+      <c r="C287" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0.0461509858577808</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B288" t="s">
+        <v>10</v>
+      </c>
+      <c r="C288" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0.0332376366234329</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B289" t="s">
+        <v>10</v>
+      </c>
+      <c r="C289" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0.0579018259575578</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B290" t="s">
+        <v>10</v>
+      </c>
+      <c r="C290" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0.00733354360289847</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B291" t="s">
+        <v>10</v>
+      </c>
+      <c r="C291" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0.0921465204336801</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B292" t="s">
+        <v>10</v>
+      </c>
+      <c r="C292" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0.0021404783421352</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B293" t="s">
+        <v>10</v>
+      </c>
+      <c r="C293" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0.0811310726550014</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B294" t="s">
+        <v>10</v>
+      </c>
+      <c r="C294" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0.0609600642819171</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>926377841</v>
+      </c>
+      <c r="B295" t="s">
+        <v>10</v>
+      </c>
+      <c r="C295" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0.0298894552037777</v>
       </c>
     </row>
   </sheetData>
